--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260624_211904.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260624_211904.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
